--- a/api/templates/Devices.xlsx
+++ b/api/templates/Devices.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22730"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROJECTS_2016\SystemOne\aspect\api\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Nicolas\Trabajo\SystemOne\Repositorios\Aspect2\aspect\api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9AC653-F01E-4550-AE61-BAC08ED4BA88}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="480" windowWidth="37920" windowHeight="17235" tabRatio="815"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Devices" sheetId="1" r:id="rId1"/>
@@ -129,9 +130,6 @@
     <t>Total Tests</t>
   </si>
   <si>
-    <t>Device Name</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -160,12 +158,15 @@
   </si>
   <si>
     <t>Aspect Devices</t>
+  </si>
+  <si>
+    <t>Device</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
@@ -367,49 +368,49 @@
     </xf>
   </cellXfs>
   <cellStyles count="43">
-    <cellStyle name="Гиперссылка" xfId="1" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="3" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="5" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="7" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="9" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="11" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="13" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="15" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="17" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="19" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="21" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="23" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="25" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="27" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="29" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="31" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="33" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="35" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="37" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="39" builtinId="8" hidden="1"/>
-    <cellStyle name="Гиперссылка" xfId="41" builtinId="8" hidden="1"/>
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="4" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="6" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="8" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="10" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="12" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="14" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="16" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="18" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="20" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="22" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="24" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="26" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="28" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="30" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="32" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="34" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="36" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="38" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="40" builtinId="9" hidden="1"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="42" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="8" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="10" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="12" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="14" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="16" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="18" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="20" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="22" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="24" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="26" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="28" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="30" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="32" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="34" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="36" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="38" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="40" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="7" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="9" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="11" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="13" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="15" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="17" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="19" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="21" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="23" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="25" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="27" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="29" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="31" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="33" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="35" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="37" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="39" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="41" builtinId="8" hidden="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -436,7 +437,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -773,7 +774,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -786,26 +787,26 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>33</v>
@@ -813,19 +814,19 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>39</v>
-      </c>
       <c r="C5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -846,7 +847,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>

--- a/api/templates/Devices.xlsx
+++ b/api/templates/Devices.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Nicolas\Trabajo\SystemOne\Repositorios\Aspect2\aspect\api\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROJECTS_2016\SystemOne\aspect\api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9AC653-F01E-4550-AE61-BAC08ED4BA88}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="480" windowWidth="37920" windowHeight="17235" tabRatio="815"/>
   </bookViews>
   <sheets>
     <sheet name="Devices" sheetId="1" r:id="rId1"/>
@@ -130,6 +129,9 @@
     <t>Total Tests</t>
   </si>
   <si>
+    <t>Device Name</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
@@ -158,15 +160,12 @@
   </si>
   <si>
     <t>Aspect Devices</t>
-  </si>
-  <si>
-    <t>Device</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
@@ -368,49 +367,49 @@
     </xf>
   </cellXfs>
   <cellStyles count="43">
-    <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="8" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="10" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="12" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="14" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="16" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="18" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="20" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="22" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="24" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="26" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="28" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="30" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="32" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="34" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="36" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="38" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="40" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="9" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="11" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="13" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="15" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="17" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="19" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="21" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="23" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="25" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="27" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="29" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="31" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="33" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="35" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="37" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="39" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="41" builtinId="8" hidden="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="3" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="5" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="7" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="9" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="11" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="13" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="15" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="17" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="19" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="21" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="23" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="25" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="27" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="29" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="31" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="33" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="35" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="37" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="39" builtinId="8" hidden="1"/>
+    <cellStyle name="Гиперссылка" xfId="41" builtinId="8" hidden="1"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="4" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="6" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="8" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="10" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="12" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="14" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="16" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="18" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="20" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="22" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="24" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="26" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="28" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="30" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="32" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="34" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="36" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="38" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="40" builtinId="9" hidden="1"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="42" builtinId="9" hidden="1"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -437,7 +436,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -774,7 +773,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -787,26 +786,26 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>33</v>
@@ -814,19 +813,19 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -847,7 +846,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
